--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7B2246E-D6DD-444D-8928-4823A1B7F45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FFFA251-F23A-40C9-B2FF-8708C41BE68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1314,7 +1314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17D8B4B-02A1-488C-8A4D-2561EF79D1D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BE4D15-152D-46E7-A881-1C1F55214BE6}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1371,7 +1371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A6E551-ED93-487B-A9FE-EC7EF38F50D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE3EE19-87D7-4F03-9338-BBBD1C0EBDD7}">
   <dimension ref="B9:O38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2221,7 +2221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DFBAFD-0DC6-4BC5-9913-868C82216232}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B2BBD5-42CF-484A-9308-9FC084C2D893}">
   <dimension ref="B9:T71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4123,7 +4123,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDF5500-F8E0-48F8-865B-B4ADA6CFAE49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB6D508-FF1F-4B0A-8527-DC66A740F138}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4167,7 +4167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268B6A7D-5A24-4BE4-BE9F-C74E346DD132}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C53089-BEB4-42D3-BC8F-B2A17AAAC3E6}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4216,7 +4216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C7C655-6B9F-4B20-A8D2-135B6D2DB686}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3EBC6E-F68A-4634-93A1-292B1461986D}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4254,7 +4254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CC7EBA-50E7-48E6-A22E-EC453DCE0856}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939564CF-15A2-40C8-A97F-3BCF46BDB489}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4300,7 +4300,7 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>0.48831666666666668</v>
+        <v>0.48831666666666673</v>
       </c>
       <c r="E12" t="s">
         <v>189</v>
@@ -4314,7 +4314,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.40083333333333332</v>
+        <v>0.40083333333333337</v>
       </c>
       <c r="E13" t="s">
         <v>189</v>
@@ -4328,7 +4328,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.41761666666666669</v>
+        <v>0.41761666666666675</v>
       </c>
       <c r="E14" t="s">
         <v>189</v>
@@ -4384,7 +4384,7 @@
         <v>37</v>
       </c>
       <c r="D18">
-        <v>0.41260000000000002</v>
+        <v>0.41259999999999991</v>
       </c>
       <c r="E18" t="s">
         <v>189</v>
@@ -4398,7 +4398,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.41924166666666673</v>
+        <v>0.41924166666666668</v>
       </c>
       <c r="E19" t="s">
         <v>189</v>
@@ -4468,7 +4468,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.39865833333333328</v>
+        <v>0.39865833333333334</v>
       </c>
       <c r="E24" t="s">
         <v>189</v>
@@ -4482,7 +4482,7 @@
         <v>37</v>
       </c>
       <c r="D25">
-        <v>0.45432500000000003</v>
+        <v>0.45432499999999992</v>
       </c>
       <c r="E25" t="s">
         <v>189</v>
@@ -4538,7 +4538,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.4378333333333333</v>
+        <v>0.43783333333333335</v>
       </c>
       <c r="E29" t="s">
         <v>189</v>
@@ -4552,7 +4552,7 @@
         <v>37</v>
       </c>
       <c r="D30">
-        <v>0.48789166666666667</v>
+        <v>0.48789166666666661</v>
       </c>
       <c r="E30" t="s">
         <v>189</v>
@@ -4622,7 +4622,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.47832500000000006</v>
+        <v>0.47832499999999994</v>
       </c>
       <c r="E35" t="s">
         <v>189</v>
@@ -4678,7 +4678,7 @@
         <v>37</v>
       </c>
       <c r="D39">
-        <v>0.4008666666666667</v>
+        <v>0.40086666666666665</v>
       </c>
       <c r="E39" t="s">
         <v>189</v>
